--- a/data/20250725_前端咖啡订单.xlsx
+++ b/data/20250725_前端咖啡订单.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W1202507251130579419</t>
+          <t>W1202507251549474067</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2025-07-25 11:30:57</t>
+          <t>2025-07-25 15:49:47</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,24 +518,20 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>备货中</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W1202507251124009271</t>
+          <t>W1202507251549414065</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -555,7 +551,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2025-07-25 11:24:00</t>
+          <t>2025-07-25 15:49:41</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -570,67 +566,167 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>备货中</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>W1202507251130579419</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>17826157137.0</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>于池</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>数智化支撑中心</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2025-07-25 11:30:57</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>咖啡测试 请勿点击</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>W1202507251124009271</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>17826157137.0</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>于池</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>数智化支撑中心</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2025-07-25 11:24:00</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>咖啡测试 请勿点击</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>W1202507251123429261</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>17826157137.0</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>于池</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>数智化支撑中心</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>2025-07-25 11:23:42</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>咖啡测试 请勿点击</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>备货中</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>nan</t>
         </is>

--- a/data/20250725_前端咖啡订单.xlsx
+++ b/data/20250725_前端咖啡订单.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W1202507251549474067</t>
+          <t>W1202507251600194423</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2025-07-25 15:49:47</t>
+          <t>2025-07-25 16:00:19</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -526,12 +526,16 @@
           <t>备货中</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W1202507251549414065</t>
+          <t>W1202507251600104416</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -551,7 +555,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2025-07-25 15:49:41</t>
+          <t>2025-07-25 16:00:10</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -574,12 +578,16 @@
           <t>备货中</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W1202507251130579419</t>
+          <t>W1202507251549474067</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -599,7 +607,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2025-07-25 11:30:57</t>
+          <t>2025-07-25 15:49:47</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -631,7 +639,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W1202507251124009271</t>
+          <t>W1202507251549414065</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -651,7 +659,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2025-07-25 11:24:00</t>
+          <t>2025-07-25 15:49:41</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -683,50 +691,154 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>W1202507251130579419</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>17826157137.0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>于池</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>数智化支撑中心</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2025-07-25 11:30:57</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>咖啡测试 请勿点击</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>W1202507251124009271</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>17826157137.0</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>于池</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>数智化支撑中心</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2025-07-25 11:24:00</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>咖啡测试 请勿点击</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>W1202507251123429261</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>17826157137.0</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>于池</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>数智化支撑中心</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>2025-07-25 11:23:42</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>咖啡测试 请勿点击</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>备货中</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>nan</t>
         </is>

--- a/data/20250725_前端咖啡订单.xlsx
+++ b/data/20250725_前端咖啡订单.xlsx
@@ -518,12 +518,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>备货中</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -570,12 +570,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>备货中</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>备货中</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
